--- a/stories/arbres/TREE-COL-020.xlsx
+++ b/stories/arbres/TREE-COL-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec maman, dans le salon. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo écoute maman. Hugo entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-020.xlsx
+++ b/stories/arbres/TREE-COL-020.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec maman, dans le salon. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo écoute maman. Hugo entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Hugo rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Hugo rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Hugo rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Hugo rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Hugo rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-020.xlsx
+++ b/stories/arbres/TREE-COL-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — dans le salon</t>
+          <t>Le coussin tiède de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le coussin du salon est tiède. Nina raconte son malaise. Puis elle joue au parc, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Hugo est avec maman, dans le salon. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo écoute maman. Hugo entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>Le coussin du canapé est encore tiède. Une chaussette pend au bras du fauteuil. La lampe fait un rond jaune sur le tapis. Le cartable de Nina est contre la table basse. Il sent le crayon et le papier. Dehors, la pluie tape le volet, tout petit. Ça sent le cacao, dans la cuisine d'à côté. Tes chaussettes, Nina. Une est déjà au chaud. Le cartable est rentré. Toi aussi. J'ai écouté la maîtresse. Un camarade a parlé tout bas. Nina pose les mains sur le tapis. Le tapis est rêche, puis doux. Son ventre se serre, tout petit. C'est un malaise. Tu as bien fait de raconter. On écoute la maîtresse, à l'école. Si malaise, on raconte à la maison. Je raconte à papa, ou à maman. En ce moment, Nina enfile sa botte. La botte est un peu froide, un peu lisse. L'autre maintenant. Elle colle un peu. Tire doucement. Bravo. Le parc nous attend, tout près. On y va ? Oui. On t'écoute, aussi dehors. La pluie a presque fini, sur le volet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Hugo est avec maman, dans le salon. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo écoute maman. Hugo entend les mots : écouter, si malaise raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le coussin du canapé est encore tiède.
+narrateur|Une chaussette pend au bras du fauteuil.
+narrateur|La lampe fait un rond jaune sur le tapis.
+narrateur|Le cartable de Nina est contre la table basse.
+narrateur|Il sent le crayon et le papier.
+narrateur|Dehors, la pluie tape le volet, tout petit.
+narrateur|Ça sent le cacao, dans la cuisine d'à côté.
+maman|Tes chaussettes, Nina.
+maman|Une est déjà au chaud.
+papa|Le cartable est rentré.
+papa|Toi aussi.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|Un camarade a parlé tout bas.
+narrateur|Nina pose les mains sur le tapis.
+narrateur|Le tapis est rêche, puis doux.
+narrateur|Son ventre se serre, tout petit.
+maman|C'est un malaise.
+maman|Tu as bien fait de raconter.
+papa|On écoute la maîtresse, à l'école.
+papa|Si malaise, on raconte à la maison.
+enfant-f|Je raconte à papa, ou à maman.
+narrateur|En ce moment, Nina enfile sa botte.
+narrateur|La botte est un peu froide, un peu lisse.
+maman|L'autre maintenant.
+enfant-f|Elle colle un peu.
+papa|Tire doucement.
+papa|Bravo.
+maman|Le parc nous attend, tout près.
+enfant-f|On y va ?
+maman|Oui.
+maman|On t'écoute, aussi dehors.
+narrateur|La pluie a presque fini, sur le volet.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Le parc a trois coins, tout proches. Le bac à sable, le toboggan, ou les balançoires ? On joue. On a déjà raconté, au salon.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,10 +1564,17 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le parc a trois coins, tout proches.
+maman|Le bac à sable, le toboggan, ou les balançoires ?
+papa|On joue.
+papa|On a déjà raconté, au salon.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1545,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le bac à sable. Le sable est frais, un peu gris. Un grain colle à son doigt. Une petite pelle attend, toute rouge. Tu as tes mains, Nina ? Elles sont froides. Ce matin, tu as écouté la maîtresse. Oui. Puis j'ai raconté, au salon. Bravo. Si malaise, tu racontes à la maison. Nina creuse un petit trou. Le sable fait un bruit sec. C'est du bon travail. Un grain brille, tout plat.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1739,28 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina va vers le bac à sable.
+narrateur|Le sable est frais, un peu gris.
+narrateur|Un grain colle à son doigt.
+narrateur|Une petite pelle attend, toute rouge.
+maman|Tu as tes mains, Nina ?
+enfant-f|Elles sont froides.
+papa|Ce matin, tu as écouté la maîtresse.
+enfant-f|Oui.
+enfant-f|Puis j'ai raconté, au salon.
+maman|Bravo.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Nina creuse un petit trou.
+narrateur|Le sable fait un bruit sec.
+papa|C'est du bon travail.
+narrateur|Un grain brille, tout plat.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina a eu un malaise. Que fait-elle, à la maison ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1945,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina a eu un malaise.
+maman|Que fait-elle, à la maison ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina essuie un grain de sable. Je raconte à papa, ou à maman. Bravo, Nina. C'est du bon travail. Le ventre se desserre, tout doucement. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2118,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+narrateur|Nina essuie un grain de sable.
+enfant-f|Je raconte à papa, ou à maman.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+narrateur|Le ventre se desserre, tout doucement.
+maman|On t'écoute.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2154,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2318,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2349,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Il est un peu sablé, tout rond. Il fait poum contre l'herbe. Tu te souviens de la classe ? J'ai écouté la maîtresse. Un camarade a parlé tout bas. Tu as raconté, au salon. C'est bien. Nina tient le ballon contre son ventre. Si malaise, tu reviens nous le dire. Oui, papa. Bravo. Le ballon a une tache de sable, toute plate. Nina est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2489,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Il est un peu sablé, tout rond.
+narrateur|Il fait poum contre l'herbe.
+papa|Tu te souviens de la classe ?
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as raconté, au salon.
+maman|C'est bien.
+narrateur|Nina tient le ballon contre son ventre.
+papa|Si malaise, tu reviens nous le dire.
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Le ballon a une tache de sable, toute plate.
+narrateur|Nina est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2536,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2704,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2735,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le ballon est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours a du sable sur le ventre, près du ballon. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,10 +2875,37 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours a du sable sur le ventre, près du ballon.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2798,7 +2930,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le ballon. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3070,17 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3108,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le ballon est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée tient le ballon, tout droit. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,10 +3248,37 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée tient le ballon, tout droit.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3134,7 +3303,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le ballon. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3443,17 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3481,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le ballon est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion a un grain dans la crinière. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,10 +3621,37 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion a un grain dans la crinière.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3470,7 +3676,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le ballon. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3816,17 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3854,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le seau. Un peu de sable tremble au fond. Le seau sonne, tout creux. Tu as écouté, ce matin. Oui. Puis j'ai raconté mon malaise. On écoute la maîtresse. Ensuite, si malaise, on raconte. Nina pose le seau près de ses genoux. Bravo, Nina. On t'écoute, à la maison. Un grain glisse le long du seau. Le seau est à moitié plein, tout gris. Nina est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,10 +3994,29 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu as écouté, ce matin.
+enfant-f|Oui.
+enfant-f|Puis j'ai raconté mon malaise.
+papa|On écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte.
+narrateur|Nina pose le seau près de ses genoux.
+maman|Bravo, Nina.
+maman|On t'écoute, à la maison.
+narrateur|Un grain glisse le long du seau.
+narrateur|Le seau est à moitié plein, tout gris.
+narrateur|Nina est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +4041,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4209,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4240,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le seau est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours regarde le seau, tout calme. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,10 +4380,37 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours regarde le seau, tout calme.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4170,7 +4435,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le seau. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4575,17 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4613,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le seau est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée a du sable dans la robe. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,10 +4753,37 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée a du sable dans la robe.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4506,7 +4808,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le seau. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4948,17 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4986,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le seau est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion a une patte dans le seau. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,10 +5126,37 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion a une patte dans le seau.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4842,7 +5181,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le seau. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5321,17 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5359,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Une oreille est encore chaude. Le tissu est râpé, tout doux. Le doudou t'écoute, lui aussi. Doudou, j'ai eu un malaise. J'ai raconté à maman. Tu as bien fait. Papa t'écoute aussi. Nina serre le doudou, tout près. On écoute la maîtresse. Si malaise, raconter à la maison. C'est du bon travail. Un grain de sable colle à l'oreille du doudou. Nina est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,7 +5499,22 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Une oreille est encore chaude.
+narrateur|Le tissu est râpé, tout doux.
+papa|Le doudou t'écoute, lui aussi.
+enfant-f|Doudou, j'ai eu un malaise.
+enfant-f|J'ai raconté à maman.
+maman|Tu as bien fait.
+maman|Papa t'écoute aussi.
+narrateur|Nina serre le doudou, tout près.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+maman|C'est du bon travail.
+narrateur|Un grain de sable colle à l'oreille du doudou.
+narrateur|Nina est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5178,7 +5542,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5710,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5741,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le doudou est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours et le doudou se touchent, tout doux. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,10 +5881,37 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours et le doudou se touchent, tout doux.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5542,7 +5936,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le doudou. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +6076,17 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +6114,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le doudou est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée caresse le doudou, tout sableux. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,10 +6254,37 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée caresse le doudou, tout sableux.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5878,7 +6309,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le doudou. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6449,17 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6487,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Près du bac à sable, Nina s'assoit. Le doudou est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion pose la tête sur le doudou. Nina reste près de le bac à sable. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,10 +6627,37 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Près du bac à sable, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion pose la tête sur le doudou.
+narrateur|Nina reste près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6214,7 +6682,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le bac à sable. Elle a tenu le doudou. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6822,17 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6860,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le toboggan. Le métal est un peu froid. Les marches sont lisses, toutes étroites. Une feuille colle en haut, toute plate. Tu montes, Nina ? Oui, papa. Tu as écouté, à l'école. La maîtresse a parlé. Un camarade a chuchoté. Tu as raconté, au salon. Mon ventre est plus calme. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina glisse, tout doux. Le vent lui chatouille les joues.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,11 +7000,28 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina va vers le toboggan.
+narrateur|Le métal est un peu froid.
+narrateur|Les marches sont lisses, toutes étroites.
+narrateur|Une feuille colle en haut, toute plate.
+papa|Tu montes, Nina ?
+enfant-f|Oui, papa.
+maman|Tu as écouté, à l'école.
+enfant-f|La maîtresse a parlé.
+enfant-f|Un camarade a chuchoté.
+papa|Tu as raconté, au salon.
+enfant-f|Mon ventre est plus calme.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+narrateur|Nina glisse, tout doux.
+narrateur|Le vent lui chatouille les joues.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6551,7 +7046,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>On écoute la maîtresse. Et si malaise, on raconte ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,7 +7206,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|On écoute la maîtresse.
+papa|Et si malaise, on raconte ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6739,7 +7235,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute. Si malaise, raconter à la maison. Nina pose les pieds dans l'herbe. J'ai raconté, au salon. Bravo. Tu as fait du bon travail. La feuille reste en haut, toute plate. On continue, tout calme.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,7 +7379,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On écoute.
+papa|Si malaise, raconter à la maison.
+narrateur|Nina pose les pieds dans l'herbe.
+enfant-f|J'ai raconté, au salon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La feuille reste en haut, toute plate.
+papa|On continue, tout calme.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6911,7 +7415,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,7 +7579,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7103,7 +7610,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Il est un peu sablé, tout rond. Il fait poum contre l'herbe. Tu te souviens de la classe ? J'ai écouté la maîtresse. Un camarade a parlé tout bas. Tu as raconté, au salon. C'est bien. Nina tient le ballon contre son ventre. Si malaise, tu reviens nous le dire. Oui, papa. Bravo. Le ballon attend en bas, tout rond. Nina est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,10 +7750,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Il est un peu sablé, tout rond.
+narrateur|Il fait poum contre l'herbe.
+papa|Tu te souviens de la classe ?
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as raconté, au salon.
+maman|C'est bien.
+narrateur|Nina tient le ballon contre son ventre.
+papa|Si malaise, tu reviens nous le dire.
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Le ballon attend en bas, tout rond.
+narrateur|Nina est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7797,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7965,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7996,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le ballon est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours attend en bas, le ballon contre lui. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,10 +8136,37 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours attend en bas, le ballon contre lui.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7635,7 +8191,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le ballon. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8331,17 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8369,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le ballon est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée a le ballon sur les genoux. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,10 +8509,37 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée a le ballon sur les genoux.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7971,7 +8564,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le ballon. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8704,17 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8742,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le ballon est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion suit le ballon des yeux. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,10 +8882,37 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion suit le ballon des yeux.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8307,7 +8937,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le ballon. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +9077,17 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +9115,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le seau. Un peu de sable tremble au fond. Le seau sonne, tout creux. Tu as écouté, ce matin. Oui. Puis j'ai raconté mon malaise. On écoute la maîtresse. Ensuite, si malaise, on raconte. Nina pose le seau près de ses genoux. Bravo, Nina. On t'écoute, à la maison. Un grain glisse le long du seau. Le seau est posé près de la dernière marche. Nina est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +9255,29 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu as écouté, ce matin.
+enfant-f|Oui.
+enfant-f|Puis j'ai raconté mon malaise.
+papa|On écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte.
+narrateur|Nina pose le seau près de ses genoux.
+maman|Bravo, Nina.
+maman|On t'écoute, à la maison.
+narrateur|Un grain glisse le long du seau.
+narrateur|Le seau est posé près de la dernière marche.
+narrateur|Nina est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +9302,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9470,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9501,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le seau est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours est assis dans le seau, trop grand. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,10 +9641,37 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours est assis dans le seau, trop grand.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9007,7 +9696,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le seau. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9836,17 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9874,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le seau est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée a le seau comme un chapeau. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,10 +10014,37 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée a le seau comme un chapeau.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9343,7 +10069,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le seau. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +10209,17 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10247,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le seau est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion écoute le son creux du seau. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,10 +10387,37 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion écoute le son creux du seau.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9679,7 +10442,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le seau. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10582,17 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10620,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Une oreille est encore chaude. Le tissu est râpé, tout doux. Le doudou t'écoute, lui aussi. Doudou, j'ai eu un malaise. J'ai raconté à maman. Tu as bien fait. Papa t'écoute aussi. Nina serre le doudou, tout près. On écoute la maîtresse. Si malaise, raconter à la maison. C'est du bon travail. Le doudou glisse un peu, sur les genoux. Nina est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,7 +10760,22 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Une oreille est encore chaude.
+narrateur|Le tissu est râpé, tout doux.
+papa|Le doudou t'écoute, lui aussi.
+enfant-f|Doudou, j'ai eu un malaise.
+enfant-f|J'ai raconté à maman.
+maman|Tu as bien fait.
+maman|Papa t'écoute aussi.
+narrateur|Nina serre le doudou, tout près.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+maman|C'est du bon travail.
+narrateur|Le doudou glisse un peu, sur les genoux.
+narrateur|Nina est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10015,7 +10803,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10971,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +11002,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le doudou est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours tient le doudou, en bas du toboggan. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,10 +11142,37 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours tient le doudou, en bas du toboggan.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10379,7 +11197,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le doudou. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11337,17 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11375,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le doudou est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée a le doudou autour du cou. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,10 +11515,37 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée a le doudou autour du cou.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10715,7 +11570,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le doudou. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11710,17 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11748,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Au pied du toboggan, Nina s'assoit. Le doudou est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion réchauffe le doudou, tout brun. Nina reste près de le toboggan. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,10 +11888,37 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Au pied du toboggan, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion réchauffe le doudou, tout brun.
+narrateur|Nina reste près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11051,7 +11943,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à le toboggan. Elle a tenu le doudou. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +12083,17 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +12121,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers les balançoires. La chaîne fait tic, tout léger. Le siège est un peu humide. Ça sent l'herbe coupée, tout près. Tu t'assoies, Nina ? Oui, maman. On t'a écoutée, au salon. J'ai eu un malaise. Puis j'ai raconté. Tu as bien fait. Papa et maman t'écoutent. Nina se balance, tout peu. Ses chaussures font un petit aller-retour. Bravo, Nina. Tu as écouté, puis raconté.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,11 +12261,28 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina va vers les balançoires.
+narrateur|La chaîne fait tic, tout léger.
+narrateur|Le siège est un peu humide.
+narrateur|Ça sent l'herbe coupée, tout près.
+maman|Tu t'assoies, Nina ?
+enfant-f|Oui, maman.
+papa|On t'a écoutée, au salon.
+enfant-f|J'ai eu un malaise.
+enfant-f|Puis j'ai raconté.
+maman|Tu as bien fait.
+maman|Papa et maman t'écoutent.
+narrateur|Nina se balance, tout peu.
+narrateur|Ses chaussures font un petit aller-retour.
+papa|Bravo, Nina.
+papa|Tu as écouté, puis raconté.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11388,7 +12307,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina a écouté, puis raconté. On raconte à papa ou maman ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,7 +12467,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina a écouté, puis raconté.
+maman|On raconte à papa ou maman ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11576,7 +12496,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On raconte à papa ou maman. La chaîne fait encore tic, tout bas. Je raconte. On t'écoute. Bravo, Nina. Tu as écouté la maîtresse. Ensuite tu as parlé, à la maison. Nina pose une main sur la chaîne froide.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,7 +12640,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo respire. Hugo retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On raconte à papa ou maman.
+narrateur|La chaîne fait encore tic, tout bas.
+enfant-f|Je raconte.
+papa|On t'écoute.
+papa|Bravo, Nina.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, à la maison.
+narrateur|Nina pose une main sur la chaîne froide.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11748,7 +12676,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, dans l'herbe. Le ballon, le seau, ou le doudou ? On joue. Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,7 +12840,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, dans l'herbe.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite on raconte, si besoin.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11940,7 +12871,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Il est un peu sablé, tout rond. Il fait poum contre l'herbe. Tu te souviens de la classe ? J'ai écouté la maîtresse. Un camarade a parlé tout bas. Tu as raconté, au salon. C'est bien. Nina tient le ballon contre son ventre. Si malaise, tu reviens nous le dire. Oui, papa. Bravo. Le ballon reste coincé sous le siège. Nina est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,10 +13011,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Il est un peu sablé, tout rond.
+narrateur|Il fait poum contre l'herbe.
+papa|Tu te souviens de la classe ?
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|Un camarade a parlé tout bas.
+maman|Tu as raconté, au salon.
+maman|C'est bien.
+narrateur|Nina tient le ballon contre son ventre.
+papa|Si malaise, tu reviens nous le dire.
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Le ballon reste coincé sous le siège.
+narrateur|Nina est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12108,7 +13058,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,7 +13226,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12304,7 +13257,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le ballon est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours a le ballon coincé sous le bras. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,10 +13397,37 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours a le ballon coincé sous le bras.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12472,7 +13452,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le ballon. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,7 +13592,17 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12640,7 +13630,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le ballon est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée regarde le ballon, tout rond. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,10 +13770,37 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée regarde le ballon, tout rond.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12808,7 +13825,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le ballon. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,7 +13965,17 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12976,7 +14003,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le ballon est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion souffle, tout doux, près du ballon. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,10 +14143,37 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le ballon est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion souffle, tout doux, près du ballon.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13144,7 +14198,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le ballon. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,7 +14338,17 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13312,7 +14376,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le seau. Un peu de sable tremble au fond. Le seau sonne, tout creux. Tu as écouté, ce matin. Oui. Puis j'ai raconté mon malaise. On écoute la maîtresse. Ensuite, si malaise, on raconte. Nina pose le seau près de ses genoux. Bravo, Nina. On t'écoute, à la maison. Un grain glisse le long du seau. Le seau penche, près de la chaîne. Nina est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,10 +14516,29 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu as écouté, ce matin.
+enfant-f|Oui.
+enfant-f|Puis j'ai raconté mon malaise.
+papa|On écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte.
+narrateur|Nina pose le seau près de ses genoux.
+maman|Bravo, Nina.
+maman|On t'écoute, à la maison.
+narrateur|Un grain glisse le long du seau.
+narrateur|Le seau penche, près de la chaîne.
+narrateur|Nina est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13480,7 +14563,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,7 +14731,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13676,7 +14762,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le seau est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours a le seau entre les pieds. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,10 +14902,37 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours a le seau entre les pieds.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13844,7 +14957,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le seau. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,7 +15097,17 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14012,7 +15135,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le seau est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée tape le seau, tout léger. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,10 +15275,37 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée tape le seau, tout léger.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14180,7 +15330,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le seau. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,7 +15470,17 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14348,7 +15508,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le seau est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le seau sonne. Le lion dresse l'oreille. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,10 +15648,38 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le seau est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le seau sonne.
+narrateur|Le lion dresse l'oreille.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14516,7 +15704,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le seau. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,7 +15844,17 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14684,7 +15882,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Une oreille est encore chaude. Le tissu est râpé, tout doux. Le doudou t'écoute, lui aussi. Doudou, j'ai eu un malaise. J'ai raconté à maman. Tu as bien fait. Papa t'écoute aussi. Nina serre le doudou, tout près. On écoute la maîtresse. Si malaise, raconter à la maison. C'est du bon travail. Le doudou se balance, tout peu. Nina est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,7 +16022,22 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Une oreille est encore chaude.
+narrateur|Le tissu est râpé, tout doux.
+papa|Le doudou t'écoute, lui aussi.
+enfant-f|Doudou, j'ai eu un malaise.
+enfant-f|J'ai raconté à maman.
+maman|Tu as bien fait.
+maman|Papa t'écoute aussi.
+narrateur|Nina serre le doudou, tout près.
+papa|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+maman|C'est du bon travail.
+narrateur|Le doudou se balance, tout peu.
+narrateur|Nina est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14852,7 +16065,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches attendent, tout sages. Tom, Léa, ou Sami ? On peut leur parler. Puis on rentre.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,7 +16233,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches attendent, tout sages.
+maman|Tom, Léa, ou Sami ?
+papa|On peut leur parler.
+papa|Puis on rentre.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15048,7 +16264,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le doudou est encore là. Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Tom, j'ai écouté la maîtresse. J'ai eu un malaise. Tu l'as dit, à la maison. Papa et maman t'écoutent. Nina caresse l'oreille de l'ours. L'ours berce le doudou, tout lentement. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,10 +16404,37 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+enfant-f|Tom, j'ai écouté la maîtresse.
+enfant-f|J'ai eu un malaise.
+maman|Tu l'as dit, à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours berce le doudou, tout lentement.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15216,7 +16459,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le doudou. Elle a parlé à l'ours Tom. Plus tard, le salon est calme. L'ours Tom s'endort contre le cartable. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,7 +16599,17 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à l'ours Tom.
+narrateur|Plus tard, le salon est calme.
+narrateur|L'ours Tom s'endort contre le cartable.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15384,7 +16637,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le doudou est encore là. Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Léa, j'ai écouté. Mon ventre était serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. Nina lisse la robe bleue. La poupée et le doudou se balancent un peu. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,10 +16777,37 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+enfant-f|Léa, j'ai écouté.
+enfant-f|Mon ventre était serré.
+papa|Ce n'est pas un secret pour nous.
+papa|Tu racontes à la maison.
+narrateur|Nina lisse la robe bleue.
+narrateur|La poupée et le doudou se balancent un peu.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15552,7 +16832,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le doudou. Elle a parlé à la poupée Léa. Plus tard, le salon est calme. La poupée Léa reste sur le coussin tiède. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,7 +16972,17 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à la poupée Léa.
+narrateur|Plus tard, le salon est calme.
+narrateur|La poupée Léa reste sur le coussin tiède.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15720,7 +17010,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
+          <t>Sous les balançoires, Nina s'assoit. Le doudou est encore là. Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sami, j'ai raconté. Un camarade a chuchoté. Tu as écouté la maîtresse. Ensuite tu as parlé, au salon. Nina range une mèche de laine. Le lion retient le doudou, tout sage. Nina reste près de les balançoires. Papa. Maman. J'ai écouté. Puis j'ai raconté. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,10 +17150,37 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Hugo a entendu : écouter, si malaise raconter à la maison. Hugo dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Sous les balançoires, Nina s'assoit.
+narrateur|Le doudou est encore là.
+narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+enfant-f|Sami, j'ai raconté.
+enfant-f|Un camarade a chuchoté.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite tu as parlé, au salon.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion retient le doudou, tout sage.
+narrateur|Nina reste près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15888,7 +17205,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué à les balançoires. Elle a tenu le doudou. Elle a parlé à le lion Sami. Plus tard, le salon est calme. Le lion Sami garde la crinière un peu mêlée. On t'écoute, à la maison. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,7 +17345,17 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué à les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé à le lion Sami.
+narrateur|Plus tard, le salon est calme.
+narrateur|Le lion Sami garde la crinière un peu mêlée.
+maman|On t'écoute, à la maison.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16050,7 +17377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +17471,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-020.xlsx
+++ b/stories/arbres/TREE-COL-020.xlsx
@@ -5008,17 +5008,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le chat rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Et toi, tu as écouté la maîtresse. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer.</t>
+          <t>Nina prend le chat rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Toi, tu étais dans la classe. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina prend le &lt;emphasis level="moderate"&gt;chat&lt;/emphasis&gt; rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Et toi, tu as écouté la maîtresse. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina prend le &lt;emphasis level="moderate"&gt;chat&lt;/emphasis&gt; rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Toi, tu étais dans la classe. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Nina prend le &lt;emphasis&gt;chat&lt;/emphasis&gt; rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Et toi, tu as écouté la maîtresse. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer. [pause]</t>
+          <t>Nina prend le &lt;emphasis&gt;chat&lt;/emphasis&gt; rayé et le seau. Elle rejoint papa, près de la haie. Papa, Sarah a parlé trop près. Je t'écoute, et maman aussi. Elle a dit que le seau était à elle. Toi, tu étais dans la classe. Oui, après, mon ventre s'est serré. Merci de nous le dire, ici. Ils retournent vers Sarah. Le seau peut servir à deux. On essaie. Le chat rayé a une griffe de sable. Je suis prête à rentrer. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
 enfant-f|Papa, Sarah a parlé trop près.
 papa|Je t'écoute, et maman aussi.
 enfant-f|Elle a dit que le seau était à elle.
-maman|Et toi, tu as écouté la maîtresse.
+maman|Toi, tu étais dans la classe.
 enfant-f|Oui, après, mon ventre s'est serré.
 papa|Merci de nous le dire, ici.
 narrateur|Ils retournent vers Sarah.
@@ -8787,17 +8787,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nina descend avec le chat rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'ai écouté la maîtresse, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos.</t>
+          <t>Nina descend avec le chat rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'étais dans la classe, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina descend avec le &lt;emphasis level="moderate"&gt;chat&lt;/emphasis&gt; rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'ai écouté la maîtresse, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina descend avec le &lt;emphasis level="moderate"&gt;chat&lt;/emphasis&gt; rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'étais dans la classe, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nina descend avec le &lt;emphasis&gt;chat&lt;/emphasis&gt; rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'ai écouté la maîtresse, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos. [pause]</t>
+          <t>Nina descend avec le &lt;emphasis&gt;chat&lt;/emphasis&gt; rayé sous le bras. Elle rejoint le banc des parents. Le ballon reste en bas, pour Sarah. Qu'est-ce que tu n'as pas pu dire ? Sarah a parlé trop près, à l'école. Pendant la classe. Oui, j'étais dans la classe, puis ça. Merci, on tient la phrase, maintenant. Sarah arrive, le ballon contre elle. Nina t'a attendue en bas. On se dit au revoir ? Au revoir, Sarah. Le chat rayé a une goutte sur le dos. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8937,7 +8937,7 @@
 maman|Qu'est-ce que tu n'as pas pu dire ?
 enfant-f|Sarah a parlé trop près, à l'école.
 papa|Pendant la classe.
-enfant-f|Oui, j'ai écouté la maîtresse, puis ça.
+enfant-f|Oui, j'étais dans la classe, puis ça.
 maman|Merci, on tient la phrase, maintenant.
 narrateur|Sarah arrive, le ballon contre elle.
 papa|Nina t'a attendue en bas.
@@ -17476,7 +17476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17589,6 +17589,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
